--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
@@ -565,64 +565,64 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.332299999999999</v>
+        <v>6.370900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6459</v>
+        <v>3.9274</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6864</v>
+        <v>2.4435</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7752000000000001</v>
+        <v>0.7978000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3727</v>
+        <v>-1.4282</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1479</v>
+        <v>2.226</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8691</v>
+        <v>2.0175</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1418</v>
+        <v>0.1771</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7274</v>
+        <v>1.8404</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0939</v>
+        <v>-1.2196</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5144</v>
+        <v>-1.6052</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2009</v>
+        <v>3.1157</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09710000000000008</v>
+        <v>0.0988</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4822</v>
+        <v>-0.4485</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5793999999999999</v>
+        <v>0.5474</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2592</v>
+        <v>3.3321</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2592</v>
+        <v>3.3321</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1563</v>
+        <v>3.9712</v>
       </c>
       <c r="E3" t="n">
-        <v>3.093</v>
+        <v>3.5389</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0634</v>
+        <v>0.4323</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.5296</v>
+        <v>-3.4957</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.8709</v>
+        <v>-3.9046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3413</v>
+        <v>0.4088</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4775</v>
+        <v>-0.1735</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3708</v>
+        <v>-0.223</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1067</v>
+        <v>0.04960000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0521</v>
+        <v>-3.3221</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.5001</v>
+        <v>-3.6815</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4479</v>
+        <v>0.3594</v>
       </c>
       <c r="P3" t="n">
-        <v>4.4013</v>
+        <v>4.2842</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4.4013</v>
+        <v>4.2842</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0646</v>
+        <v>2.9737</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3915</v>
+        <v>0.4319999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>2.673</v>
+        <v>2.5417</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2201</v>
+        <v>0.209</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1789</v>
+        <v>3.2806</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.9588</v>
+        <v>-3.0716</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9692</v>
+        <v>3.9522</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8576</v>
+        <v>2.0795</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1116</v>
+        <v>1.8726</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4112</v>
+        <v>-0.4126</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1935</v>
+        <v>-1.1874</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7824</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7472000000000001</v>
+        <v>0.8740999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0146</v>
+        <v>0.07959999999999995</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7617999999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1584</v>
+        <v>-1.2868</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1789</v>
+        <v>-1.267</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02060000000000001</v>
+        <v>-0.0197</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2198</v>
+        <v>-0.2194</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2889</v>
+        <v>-0.263</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0437</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3996</v>
+        <v>2.4422</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3996</v>
+        <v>2.4422</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4696</v>
+        <v>3.5048</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2107</v>
+        <v>5.678</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7411</v>
+        <v>-2.1732</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4771000000000001</v>
+        <v>0.5310000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9990000000000001</v>
+        <v>1.0823</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5219</v>
+        <v>-0.5513</v>
       </c>
       <c r="J5" t="n">
-        <v>3.472</v>
+        <v>3.7585</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8282</v>
+        <v>3.0611</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6437</v>
+        <v>0.6973</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9948</v>
+        <v>-3.2274</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8292</v>
+        <v>-1.9789</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1656</v>
+        <v>-1.2485</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4009</v>
+        <v>3.3105</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0724</v>
+        <v>1.0569</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1003</v>
+        <v>0.1384</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9721</v>
+        <v>0.9184000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2806</v>
+        <v>-0.2252</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8388</v>
+        <v>2.9495</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.1194</v>
+        <v>-3.1747</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.888</v>
+        <v>2.784</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8016</v>
+        <v>4.1139</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9135</v>
+        <v>-1.3299</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5621</v>
+        <v>1.5789</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4157</v>
+        <v>2.4169</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8535999999999999</v>
+        <v>-0.8379000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6281</v>
+        <v>4.872199999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5805</v>
+        <v>4.734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04759999999999998</v>
+        <v>0.1383</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.066</v>
+        <v>-3.2933</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1648</v>
+        <v>-2.317</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9012</v>
+        <v>-0.9762</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4006</v>
+        <v>2.3368</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R6" t="n">
-        <v>3.601</v>
+        <v>3.5052</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3248</v>
+        <v>1.3103</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7139</v>
+        <v>0.7411</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6109</v>
+        <v>0.5690999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3996</v>
+        <v>-2.4421</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.0595</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="7">
@@ -955,37 +955,37 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5467</v>
+        <v>1.5225</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7264</v>
+        <v>0.7587</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8203</v>
+        <v>0.7638</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2225</v>
+        <v>-0.2032</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2225</v>
+        <v>-0.2032</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2417</v>
+        <v>0.2797</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2417</v>
+        <v>0.2797</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1000,22 +1000,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7489</v>
+        <v>0.7325</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4846</v>
+        <v>0.479</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2643</v>
+        <v>0.2535</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0203</v>
+        <v>0.9932</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.0203</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="8">
@@ -1033,31 +1033,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1111,31 +1111,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.395</v>
+        <v>0.3356</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3312</v>
+        <v>-0.3097</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7262</v>
+        <v>0.6453</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4119</v>
+        <v>0.3588</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1374</v>
+        <v>-0.1663</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="J10" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="K10" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2919</v>
+        <v>0.2356</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2574</v>
+        <v>-0.2895</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.497</v>
+        <v>-0.4853</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4512</v>
+        <v>-0.4328</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0458</v>
+        <v>-0.0524</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="11">
@@ -1267,37 +1267,37 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0649</v>
+        <v>-0.0822</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0245</v>
+        <v>-0.0213</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0405</v>
+        <v>-0.0609</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2243</v>
+        <v>-0.2371</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1807</v>
+        <v>-0.1762</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1163</v>
+        <v>-0.1144</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8994</v>
+        <v>-0.7879</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4366</v>
+        <v>0.07479999999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4628000000000001</v>
+        <v>-0.8626999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5479</v>
+        <v>1.626</v>
       </c>
       <c r="H12" t="n">
-        <v>0.871</v>
+        <v>0.8815999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6768000000000001</v>
+        <v>0.7444</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3359</v>
+        <v>3.6547</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3644</v>
+        <v>3.5486</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.02860000000000007</v>
+        <v>0.1061000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.788</v>
+        <v>-2.0287</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4934</v>
+        <v>-2.667</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7054</v>
+        <v>0.6383</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R12" t="n">
-        <v>3.801</v>
+        <v>3.7</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5276</v>
+        <v>-1.4655</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7710999999999999</v>
+        <v>-0.7116</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7565000000000001</v>
+        <v>-0.7538999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1771</v>
+        <v>-1.2599</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8411</v>
+        <v>1.1497</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0182</v>
+        <v>-2.4096</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8462999999999999</v>
+        <v>0.8683</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4401</v>
+        <v>-2.4482</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2864</v>
+        <v>3.3166</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9910000000000001</v>
+        <v>1.1629</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9325</v>
+        <v>-0.8311999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9235</v>
+        <v>1.9941</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1446</v>
+        <v>-0.2946</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5075</v>
+        <v>-1.617</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3629</v>
+        <v>1.3224</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8002</v>
+        <v>0.779</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5555</v>
+        <v>0.5471</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1313</v>
+        <v>0.1541</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4242</v>
+        <v>0.3928</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.3792</v>
+        <v>-3.4542</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7194</v>
+        <v>1.7801</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.0985</v>
+        <v>-5.2342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.9154</v>
+        <v>-1.453</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2708</v>
+        <v>-1.2925</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3555</v>
+        <v>-0.1605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.282</v>
+        <v>1.4682</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2391</v>
+        <v>3.3253</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.9571</v>
+        <v>-1.8571</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7067</v>
+        <v>4.216699999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>5.847300000000001</v>
+        <v>6.160600000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.1407</v>
+        <v>-1.944</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4247</v>
+        <v>-2.7484</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6083</v>
+        <v>-2.8353</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1836</v>
+        <v>0.08700000000000002</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.2015</v>
+        <v>-5.0631</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.2026</v>
+        <v>-8.9579</v>
       </c>
       <c r="R14" t="n">
-        <v>4.0012</v>
+        <v>3.8948</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7351</v>
+        <v>-1.6786</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0936</v>
+        <v>-1.9944</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3585</v>
+        <v>0.3158</v>
       </c>
       <c r="V14" t="n">
-        <v>3.7391</v>
+        <v>3.8205</v>
       </c>
       <c r="W14" t="n">
-        <v>5.3187</v>
+        <v>5.4431</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5795</v>
+        <v>-1.6226</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.5884</v>
+        <v>-3.6261</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.3244</v>
+        <v>-4.8653</v>
       </c>
       <c r="F15" t="n">
-        <v>1.736</v>
+        <v>1.2392</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8386</v>
+        <v>-0.9482999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09919999999999995</v>
+        <v>-0.1586000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7393</v>
+        <v>-0.7897</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0071</v>
+        <v>1.1489</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8452</v>
+        <v>0.9621999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1619</v>
+        <v>0.1865</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8456</v>
+        <v>-2.0972</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9444</v>
+        <v>-1.1209</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9012</v>
+        <v>-0.9762000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.0018</v>
+        <v>-5.842</v>
       </c>
       <c r="R15" t="n">
-        <v>3.601</v>
+        <v>3.5052</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6710999999999999</v>
+        <v>0.6523</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0289</v>
+        <v>-0.9589</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6999</v>
+        <v>1.6111</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0203</v>
+        <v>-0.9931000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6990999999999999</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7194</v>
+        <v>-1.7801</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.5296</v>
+        <v>-5.638199999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.289099999999999</v>
+        <v>-2.8721</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2406</v>
+        <v>-2.7661</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.3689</v>
+        <v>-5.3985</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2453000000000001</v>
+        <v>-0.3464</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.1235</v>
+        <v>-5.0521</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.459</v>
+        <v>-2.2133</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6414</v>
+        <v>1.7166</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.1004</v>
+        <v>-3.9298</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9097</v>
+        <v>-3.1853</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8867</v>
+        <v>-2.063</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0231</v>
+        <v>-1.1222</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2007</v>
+        <v>-2.1421</v>
       </c>
       <c r="R16" t="n">
-        <v>3.401</v>
+        <v>3.3106</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4385</v>
+        <v>0.4235</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0289</v>
+        <v>-0.9589</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4675</v>
+        <v>1.3824</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>10.78209999999999</v>
+        <v>10.8097</v>
       </c>
       <c r="E17" t="n">
-        <v>8.699499999999999</v>
+        <v>13.1758</v>
       </c>
       <c r="F17" t="n">
-        <v>2.082700000000002</v>
+        <v>-2.3662</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4928</v>
+        <v>-2.2506</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3211</v>
+        <v>-2.414400000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1715</v>
+        <v>0.1637000000000004</v>
       </c>
       <c r="J17" t="n">
-        <v>18.4221</v>
+        <v>20.9779</v>
       </c>
       <c r="K17" t="n">
-        <v>18.2926</v>
+        <v>19.7885</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1292999999999997</v>
+        <v>1.189299999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.9144</v>
+        <v>-23.2283</v>
       </c>
       <c r="N17" t="n">
-        <v>-20.61360000000001</v>
+        <v>-22.2028</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3008999999999999</v>
+        <v>-1.0251</v>
       </c>
       <c r="P17" t="n">
-        <v>8.0021</v>
+        <v>7.789499999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-28.0081</v>
+        <v>-27.2631</v>
       </c>
       <c r="R17" t="n">
-        <v>36.0102</v>
+        <v>35.0525</v>
       </c>
       <c r="S17" t="n">
-        <v>3.812700000000001</v>
+        <v>3.7701</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.3877</v>
+        <v>-3.8853</v>
       </c>
       <c r="U17" t="n">
-        <v>8.200199999999999</v>
+        <v>7.655200000000002</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4594</v>
+        <v>1.500800000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>22.6729</v>
+        <v>23.3465</v>
       </c>
       <c r="X17" t="n">
-        <v>-21.2133</v>
+        <v>-21.8458</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.370900000000001</v>
+        <v>6.8215</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9274</v>
+        <v>4.3501</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4435</v>
+        <v>2.4714</v>
       </c>
       <c r="G2" t="n">
         <v>0.7978000000000001</v>
@@ -610,13 +610,13 @@
         <v>3.1157</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0988</v>
+        <v>0.5494000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4485</v>
+        <v>-0.02579999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5474</v>
+        <v>0.5751999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>3.3321</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9712</v>
+        <v>4.1801</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5389</v>
+        <v>2.5022</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4323</v>
+        <v>1.6779</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.4957</v>
+        <v>-0.4126</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.9046</v>
+        <v>-1.1874</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4088</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1735</v>
+        <v>0.8740999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.223</v>
+        <v>0.07959999999999995</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04960000000000001</v>
+        <v>0.7945</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3221</v>
+        <v>-1.2868</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.6815</v>
+        <v>-1.267</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3594</v>
+        <v>-0.0197</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2842</v>
+        <v>2.1421</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>4.2842</v>
+        <v>3.1158</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9737</v>
+        <v>0.008500000000000008</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4319999999999999</v>
+        <v>0.1597</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5417</v>
+        <v>-0.1512</v>
       </c>
       <c r="V3" t="n">
-        <v>0.209</v>
+        <v>2.4422</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2806</v>
+        <v>2.4422</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.0716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RIERA PERETO</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9522</v>
+        <v>3.5226</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0795</v>
+        <v>5.6402</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8726</v>
+        <v>-2.1176</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4126</v>
+        <v>0.5310000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1874</v>
+        <v>1.0823</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7747000000000001</v>
+        <v>-0.5513</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8740999999999999</v>
+        <v>3.7585</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07959999999999995</v>
+        <v>3.0611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7945</v>
+        <v>0.6973</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2868</v>
+        <v>-3.2274</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.267</v>
+        <v>-1.9789</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0197</v>
+        <v>-1.2485</v>
       </c>
       <c r="P4" t="n">
         <v>2.1421</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1158</v>
+        <v>3.3105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2194</v>
+        <v>1.0748</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.263</v>
+        <v>0.1006</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0437</v>
+        <v>0.9742</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4422</v>
+        <v>-0.2252</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4422</v>
+        <v>2.9495</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-3.1747</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5048</v>
+        <v>2.4495</v>
       </c>
       <c r="E5" t="n">
-        <v>5.678</v>
+        <v>3.1025</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1732</v>
+        <v>-0.6529999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5310000000000001</v>
+        <v>-3.4957</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0823</v>
+        <v>-3.9046</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5513</v>
+        <v>0.4088</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7585</v>
+        <v>-0.1735</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0611</v>
+        <v>-0.223</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6973</v>
+        <v>0.04960000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2274</v>
+        <v>-3.3221</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9789</v>
+        <v>-3.6815</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2485</v>
+        <v>0.3594</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1421</v>
+        <v>4.2842</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3105</v>
+        <v>4.2842</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0569</v>
+        <v>1.452</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1384</v>
+        <v>-0.0046</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9184000000000001</v>
+        <v>1.4566</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2252</v>
+        <v>0.209</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9495</v>
+        <v>3.2806</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.1747</v>
+        <v>-3.0716</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.784</v>
+        <v>2.1056</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1139</v>
+        <v>3.2408</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3299</v>
+        <v>-1.1351</v>
       </c>
       <c r="G6" t="n">
         <v>1.5789</v>
@@ -922,13 +922,13 @@
         <v>3.5052</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3103</v>
+        <v>0.632</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7411</v>
+        <v>-0.1319</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5690999999999999</v>
+        <v>0.7639</v>
       </c>
       <c r="V6" t="n">
         <v>-2.4421</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5225</v>
+        <v>1.0403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7587</v>
+        <v>0.36</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7638</v>
+        <v>0.6803</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2032</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7325</v>
+        <v>0.2503</v>
       </c>
       <c r="T7" t="n">
-        <v>0.479</v>
+        <v>0.0803</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2535</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
         <v>0.9932</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3356</v>
+        <v>0.5527</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3097</v>
+        <v>-0.1482</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6453</v>
+        <v>0.7009</v>
       </c>
       <c r="G10" t="n">
         <v>0.3588</v>
@@ -1234,13 +1234,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4853</v>
+        <v>-0.2681</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4328</v>
+        <v>-0.2713</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0524</v>
+        <v>0.0032</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1221</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0822</v>
+        <v>0.09860000000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0213</v>
+        <v>0.09870000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0609</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2371</v>
+        <v>1.626</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2776</v>
+        <v>0.8815999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0405</v>
+        <v>0.7444</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0405</v>
+        <v>3.6547</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3.5486</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>0.1061000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2776</v>
+        <v>-2.0287</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2776</v>
+        <v>-2.667</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.6383</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.3895000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.0895</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1762</v>
+        <v>-0.5789</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0618</v>
+        <v>-0.6875</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1144</v>
+        <v>0.1086</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3311</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3311</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7879</v>
+        <v>0.05630000000000024</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07479999999999998</v>
+        <v>-0.3953000000000007</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8626999999999999</v>
+        <v>0.4517</v>
       </c>
       <c r="G12" t="n">
-        <v>1.626</v>
+        <v>1.4682</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8815999999999999</v>
+        <v>3.3253</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7444</v>
+        <v>-1.8571</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6547</v>
+        <v>4.216699999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5486</v>
+        <v>6.160600000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1061000000000001</v>
+        <v>-1.944</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0287</v>
+        <v>-2.7484</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.667</v>
+        <v>-2.8353</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6383</v>
+        <v>0.08700000000000002</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3895000000000001</v>
+        <v>-5.0631</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.0895</v>
+        <v>-8.9579</v>
       </c>
       <c r="R12" t="n">
-        <v>3.7</v>
+        <v>3.8948</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4655</v>
+        <v>-0.1693</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7116</v>
+        <v>-1.0973</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7538999999999999</v>
+        <v>0.9279999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5590000000000001</v>
+        <v>3.8205</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2211</v>
+        <v>5.4431</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.78</v>
+        <v>-1.6226</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2599</v>
+        <v>-0.0544</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1497</v>
+        <v>-0.0213</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4096</v>
+        <v>-0.0331</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8683</v>
+        <v>-0.2371</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4482</v>
+        <v>-0.2776</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3166</v>
+        <v>0.0405</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1629</v>
+        <v>0.0405</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8311999999999999</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9941</v>
+        <v>0.0405</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2946</v>
+        <v>-0.2776</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.617</v>
+        <v>-0.2776</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3224</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.779</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7263</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5471</v>
+        <v>-0.1484</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1541</v>
+        <v>-0.0618</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3928</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.4542</v>
+        <v>0.3311</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7801</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.2342</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.453</v>
+        <v>-1.6013</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2925</v>
+        <v>0.6134999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1605</v>
+        <v>-2.2149</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4682</v>
+        <v>0.8683</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3253</v>
+        <v>-2.4482</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8571</v>
+        <v>3.3166</v>
       </c>
       <c r="J14" t="n">
-        <v>4.216699999999999</v>
+        <v>1.1629</v>
       </c>
       <c r="K14" t="n">
-        <v>6.160600000000001</v>
+        <v>-0.8311999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.944</v>
+        <v>1.9941</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7484</v>
+        <v>-0.2946</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.8353</v>
+        <v>-1.617</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08700000000000002</v>
+        <v>1.3224</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.0631</v>
+        <v>0.779</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.9579</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>3.8948</v>
+        <v>2.7263</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6786</v>
+        <v>0.2056</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9944</v>
+        <v>-0.3821</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3158</v>
+        <v>0.5877</v>
       </c>
       <c r="V14" t="n">
-        <v>3.8205</v>
+        <v>-3.4542</v>
       </c>
       <c r="W14" t="n">
-        <v>5.4431</v>
+        <v>1.7801</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6226</v>
+        <v>-5.2342</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.6261</v>
+        <v>-3.3279</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.8653</v>
+        <v>-4.2054</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2392</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9482999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>3.5052</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6523</v>
+        <v>0.9503999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>-0.299</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6111</v>
+        <v>1.2494</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9931000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.638199999999999</v>
+        <v>-5.3222</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8721</v>
+        <v>-2.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7661</v>
+        <v>-3.0721</v>
       </c>
       <c r="G16" t="n">
         <v>-5.3985</v>
@@ -1702,13 +1702,13 @@
         <v>3.3106</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4235</v>
+        <v>0.7395</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9589</v>
+        <v>-0.3369</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3824</v>
+        <v>1.0763</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8316</v>
@@ -1735,10 +1735,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>10.8097</v>
+        <v>11.7372</v>
       </c>
       <c r="E17" t="n">
-        <v>13.1758</v>
+        <v>14.1036</v>
       </c>
       <c r="F17" t="n">
         <v>-2.3662</v>
@@ -1747,10 +1747,10 @@
         <v>-2.2506</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.414400000000001</v>
+        <v>-2.4144</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1637000000000004</v>
+        <v>0.1636999999999995</v>
       </c>
       <c r="J17" t="n">
         <v>20.9779</v>
@@ -1759,7 +1759,7 @@
         <v>19.7885</v>
       </c>
       <c r="L17" t="n">
-        <v>1.189299999999999</v>
+        <v>1.1893</v>
       </c>
       <c r="M17" t="n">
         <v>-23.2283</v>
@@ -1780,13 +1780,13 @@
         <v>35.0525</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7701</v>
+        <v>4.697799999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.8853</v>
+        <v>-2.9576</v>
       </c>
       <c r="U17" t="n">
-        <v>7.655200000000002</v>
+        <v>7.6554</v>
       </c>
       <c r="V17" t="n">
         <v>1.500800000000001</v>
